--- a/OpenCode for Excel.xlsx
+++ b/OpenCode for Excel.xlsx
@@ -17,7 +17,7 @@
 
 <file path=xl/webextensions/webextension.xml><?xml version="1.0" encoding="utf-8"?>
 <we:webextension xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{3f7c1d92-6a41-4f0e-9c55-8b27e0d4a1c6}">
-  <we:reference id="3f7c1d92-6a41-4f0e-9c55-8b27e0d4a1c6" version="1.0.0.0" store="developer" storeType="Registry"/>
+  <we:reference id="3f7c1d92-6a41-4f0e-9c55-8b27e0d4a1c6" version="1.2.0.0" store="developer" storeType="Registry"/>
   <we:alternateReferences/>
   <we:properties/>
   <we:bindings/>
